--- a/templates/KTS-Inkooporder-template-RevA.xlsx
+++ b/templates/KTS-Inkooporder-template-RevA.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="164" formatCode="€ #,##0.00"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -31,7 +31,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0007567F"/>
-      <sz val="24"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -63,11 +63,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="005C6675"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005C6675"/>
+      <color rgb="000F1B2D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -80,19 +81,19 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -120,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -164,6 +165,17 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCDCDC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCDCDC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="00DCDCDC"/>
       </right>
@@ -179,57 +191,80 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -310,12 +345,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>0</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="904875" cy="600075"/>
+    <ext cx="209550" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -323,6 +358,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="800100" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -625,449 +685,517 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INKOOPORDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="F4" s="2" t="inlineStr">
+          <t xml:space="preserve">  INKOOPORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Nieuwboerweg 2A, 1738BB Waarland</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>+31 6 5123 9050  -  info@kuijpers-ts.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="12" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="6">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>+31 6 5123 9050  ·  info@kuijpers-ts.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>SCHEIDINGSTEKEN</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>DATUM</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>PO-NUMMER</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>[Projectcode]</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>[DD-MM-JJJJ]</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>[Auto]</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="G9" s="4" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>LEVERANCIER</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>LEVERADRES</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>[Bedrijfsnaam leverancier]</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Kuijpers Technical Services BV</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>[Contactpersoon]</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Crediteurenadministratie</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>[Adres]</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
+          <t>[Contactpersoon]</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Nieuwboerweg 2A</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+          <t>Crediteurenadministratie</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>[Postcode + plaats]</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
+          <t>[Adres]</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>1738BB, Waarland</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+          <t>Nieuwboerweg 2A</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>[Telefoon  -  E-mail]</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
+          <t>[Postcode + plaats]</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>+31 6 5123 9050  -  info@kuijpers-ts.nl</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+          <t>1738BB, Waarland</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>[Telefoon]</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>+31 6 5123 9050</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>[E-mail]</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>info@kuijpers-ts.nl</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>ITEM #</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>OMSCHRIJVING</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>AANTAL</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>EENHEID</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>PRIJS / STUK</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>TOTAAL</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="12" t="n">
+      <c r="G19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15">
-        <f>IFERROR(D18*F18,"")</f>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="17">
+        <f>IFERROR(D20*E20,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="12" t="n">
+      <c r="G20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15">
-        <f>IFERROR(D19*F19,"")</f>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="17">
+        <f>IFERROR(D21*E21,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="12" t="n">
+      <c r="G21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15">
-        <f>IFERROR(D20*F20,"")</f>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="17">
+        <f>IFERROR(D22*E22,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="12" t="n">
+      <c r="G22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15">
-        <f>IFERROR(D21*F21,"")</f>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="17">
+        <f>IFERROR(D23*E23,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="12" t="n">
+      <c r="G23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15">
-        <f>IFERROR(D22*F22,"")</f>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="17">
+        <f>IFERROR(D24*E24,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="n">
+      <c r="G24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15">
-        <f>IFERROR(D23*F23,"")</f>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="17">
+        <f>IFERROR(D25*E25,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="12" t="n">
+      <c r="G25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15">
-        <f>IFERROR(D24*F24,"")</f>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="17">
+        <f>IFERROR(D26*E26,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="12" t="n">
+      <c r="G26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15">
-        <f>IFERROR(D25*F25,"")</f>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="17">
+        <f>IFERROR(D27*E27,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="G27" s="14" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>OPMERKINGEN OF SPECIALE INSTRUCTIES</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Subtotaal</t>
         </is>
       </c>
-      <c r="G26" s="18">
-        <f>SUM(G18:G25)</f>
+      <c r="F29" s="20">
+        <f>SUM(F20:F27)</f>
         <v/>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>[Vul opmerkingen in...]</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>BTW (21%)</t>
         </is>
       </c>
-      <c r="G27" s="18">
-        <f>G26*0.21</f>
+      <c r="F30" s="20">
+        <f>F29*0.21</f>
         <v/>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="n"/>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="19" t="inlineStr">
         <is>
           <t>Overige</t>
         </is>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="F32" s="20" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>BETALINGSTERMIJN</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>TOTAAL</t>
+        </is>
+      </c>
+      <c r="F33" s="25">
+        <f>F29+F30+F31+F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>30 dagen na factuurdatum</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>TOTAAL</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="26">
-        <f>G26+G27+G28+G29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Op deze inkooporder zijn de Algemene Voorwaarden 2026 van Kuijpers Technical Services BV van toepassing.</t>
         </is>
       </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>KvK 93410557  ·  BTW NL866385368B01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="F4:G4"/>
+  <mergeCells count="54">
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="D12:G12"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E6:G6"/>
     <mergeCell ref="D14:G14"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A27:D29"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
